--- a/Documentos/Documentos Excel - Hojas de calculo/Funciones financieras.xlsx
+++ b/Documentos/Documentos Excel - Hojas de calculo/Funciones financieras.xlsx
@@ -12,14 +12,13 @@
     <workbookView xWindow="34455" yWindow="7590" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
-    <sheet name="Funciones financiera" sheetId="46" r:id="rId1"/>
-    <sheet name="Valor Futuro(VF)" sheetId="34" r:id="rId2"/>
-    <sheet name="Pago" sheetId="50" r:id="rId3"/>
-    <sheet name="Tasa" sheetId="51" r:id="rId4"/>
-    <sheet name="Numero de periodos(NPER)" sheetId="52" r:id="rId5"/>
-    <sheet name="Valor actual(VA)" sheetId="55" r:id="rId6"/>
-    <sheet name="Tasa interna de retorno(TIR)" sheetId="56" r:id="rId7"/>
-    <sheet name="Ejecicio Formulas financieras" sheetId="49" r:id="rId8"/>
+    <sheet name="Valor Futuro(VF)" sheetId="34" r:id="rId1"/>
+    <sheet name="Pago" sheetId="50" r:id="rId2"/>
+    <sheet name="Tasa" sheetId="51" r:id="rId3"/>
+    <sheet name="Numero de periodos(NPER)" sheetId="52" r:id="rId4"/>
+    <sheet name="Valor actual(VA)" sheetId="55" r:id="rId5"/>
+    <sheet name="Tasa interna de retorno(TIR)" sheetId="56" r:id="rId6"/>
+    <sheet name="Ejecicio Formulas financieras" sheetId="49" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="Cantidad">#REF!</definedName>
@@ -57,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
   <si>
     <r>
       <t xml:space="preserve">Tu empresa planea </t>
@@ -795,27 +794,35 @@
     <t>Formula</t>
   </si>
   <si>
-    <t>Calculo erroneo</t>
-  </si>
-  <si>
-    <t>VAN o valor actual neto</t>
-  </si>
-  <si>
     <t>Que proyecto me paga mas que la tasa</t>
   </si>
   <si>
-    <t>Valor</t>
+    <t>Inversión</t>
+  </si>
+  <si>
+    <t>A pagar:</t>
+  </si>
+  <si>
+    <t>Tasa de interes:</t>
+  </si>
+  <si>
+    <t>Cantidad de cuotas:</t>
+  </si>
+  <si>
+    <t>VAN o valor actual neto(ganancia de inversion)</t>
+  </si>
+  <si>
+    <t>Capital prestado</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -981,11 +988,8 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1004,13 +1008,25 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1020,15 +1036,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1052,55 +1059,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>784280</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="13357280" cy="6200774"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1823,7 +1781,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2720,7 +2678,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3212,15 +3170,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>269876</xdr:colOff>
+      <xdr:colOff>269875</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>690563</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>111125</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>206374</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>55562</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3229,8 +3187,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11350626" y="658813"/>
-          <a:ext cx="1262062" cy="428625"/>
+          <a:off x="11644313" y="658813"/>
+          <a:ext cx="1619249" cy="738187"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3266,7 +3224,15 @@
         <a:p>
           <a:r>
             <a:rPr lang="es-AR" sz="1100"/>
-            <a:t>El vf va en negativo.</a:t>
+            <a:t>El va va en negativo porque es</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-AR" sz="1100" baseline="0"/>
+            <a:t> una deuda</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-AR" sz="1100"/>
+            <a:t>.</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3276,7 +3242,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3796,7 +3762,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -4558,16 +4524,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>205154</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>124558</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>505558</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>109904</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>549520</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>161193</xdr:rowOff>
+      <xdr:colOff>14655</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>146538</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4576,7 +4542,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4381500" y="1817077"/>
+          <a:off x="3846635" y="1985596"/>
           <a:ext cx="1179635" cy="586154"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4613,7 +4579,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="es-AR" sz="1100"/>
-            <a:t>Utilizar la formula abs en b8</a:t>
+            <a:t>Utilizar la formula abs en(b8)</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4623,7 +4589,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5328,9 +5294,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="B3:L10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
+    <col min="12" max="12" width="17.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:12" ht="17.25">
+      <c r="B3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="L4" s="22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="17.25">
+      <c r="B5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="23">
+        <v>8080556</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="15.75">
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="15">
+      <c r="L9" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="15.75">
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+      <c r="L10" s="24"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -5338,48 +5345,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:L10"/>
+  <dimension ref="B1:L5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="21.875" customWidth="1"/>
-    <col min="12" max="12" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="17.25">
-      <c r="B3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+    <row r="1" spans="2:12" ht="17.25">
+      <c r="B1" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="4" spans="2:12">
-      <c r="L4" s="31" t="s">
-        <v>42</v>
+    <row r="3" spans="2:12" ht="15">
+      <c r="B3" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="17.25">
-      <c r="B5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="32">
-        <v>8080556</v>
+    <row r="4" spans="2:12" ht="15">
+      <c r="B4" s="2"/>
+      <c r="L4" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15.75">
-      <c r="B7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="15">
-      <c r="L9" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="15.75">
-      <c r="C10" t="s">
-        <v>2</v>
-      </c>
-      <c r="L10" s="33"/>
+    <row r="5" spans="2:12" ht="15">
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5389,30 +5381,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:L5"/>
+  <dimension ref="B1:M5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="11" max="11" width="12.875" customWidth="1"/>
+    <col min="13" max="13" width="14.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="17.25">
+    <row r="1" spans="2:13" ht="17.25">
       <c r="B1" s="3" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="15">
+    <row r="3" spans="2:13" ht="15">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="15">
+    <row r="4" spans="2:13" ht="15">
       <c r="B4" s="2"/>
-      <c r="L4" s="10" t="s">
-        <v>38</v>
+      <c r="M4" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="15">
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="33"/>
+    <row r="5" spans="2:13" ht="15">
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M5" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5422,44 +5418,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:M5"/>
+  <dimension ref="B1:L6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="11" max="11" width="12.875" customWidth="1"/>
+    <col min="12" max="12" width="18.875" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="2:13" ht="17.25">
-      <c r="B1" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" ht="15">
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" ht="15">
-      <c r="B4" s="2"/>
-      <c r="M4" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" ht="15">
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M5" s="34"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:L6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="2:12" ht="17.25">
       <c r="B1" s="3" t="s">
@@ -5471,36 +5434,36 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="15">
+    <row r="4" spans="2:12" ht="15" customHeight="1">
       <c r="B4" s="2"/>
       <c r="L4" s="10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="5" spans="2:12">
-      <c r="B5" s="28" t="s">
+    <row r="5" spans="2:12" ht="14.25" customHeight="1">
+      <c r="B5" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="L5" s="35"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="L5" s="26"/>
     </row>
     <row r="6" spans="2:12">
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5511,7 +5474,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:N11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" outlineLevelCol="1"/>
@@ -5529,70 +5492,67 @@
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
     </row>
     <row r="4" spans="2:8">
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
     </row>
     <row r="5" spans="2:8">
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
     </row>
     <row r="6" spans="2:8">
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
     </row>
     <row r="8" spans="2:8">
-      <c r="B8" s="23">
-        <f>PV(5%,5,2000)</f>
-        <v>-8658.953341261642</v>
-      </c>
+      <c r="B8" s="31"/>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="2:8">
-      <c r="B11" s="24">
+      <c r="B11" s="32">
         <f>2000*5</f>
         <v>10000</v>
       </c>
-      <c r="D11" s="26"/>
+      <c r="D11" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5603,7 +5563,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:K18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" outlineLevelCol="1"/>
@@ -5623,30 +5583,30 @@
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
     </row>
     <row r="4" spans="2:9">
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
     </row>
     <row r="5" spans="2:9">
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="2:9">
       <c r="C6" t="s">
@@ -5654,113 +5614,113 @@
       </c>
     </row>
     <row r="11" spans="2:9" ht="25.5">
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="21" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="25.5">
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="18">
         <v>-15500</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="18">
         <v>-18400</v>
       </c>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
     </row>
     <row r="13" spans="2:9" ht="15">
-      <c r="C13" s="18">
+      <c r="C13" s="15">
         <v>1</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="15">
         <v>6000</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="15">
         <v>11500</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="I13" s="25" t="s">
-        <v>41</v>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="I13" s="20" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="2:9">
-      <c r="C14" s="18">
+      <c r="C14" s="15">
         <v>2</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="15">
         <v>7500</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="15">
         <v>9500</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
       <c r="I14" s="11" t="e">
         <f>INDEX(F11:G12,1,MATCH(40%,F12:G12,-1))</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="15" spans="2:9">
-      <c r="C15" s="18">
+      <c r="C15" s="15">
         <v>3</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="15">
         <v>9800</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="15">
         <v>7700</v>
       </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
     </row>
     <row r="16" spans="2:9">
-      <c r="C16" s="18">
+      <c r="C16" s="15">
         <v>4</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="15">
         <v>10500</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="15">
         <v>6500</v>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
     </row>
     <row r="17" spans="3:7">
-      <c r="C17" s="18">
+      <c r="C17" s="15">
         <v>5</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="15">
         <v>11000</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="15">
         <v>4500</v>
       </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
     </row>
     <row r="18" spans="3:7">
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5771,13 +5731,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="21.875" customWidth="1"/>
-    <col min="9" max="9" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5821,14 +5781,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="I14" s="12"/>
-      <c r="K14" s="13"/>
+      <c r="I14" s="27"/>
+      <c r="K14" s="12"/>
     </row>
     <row r="15" spans="2:11" ht="15">
       <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K15" s="14"/>
+      <c r="K15" s="13"/>
     </row>
     <row r="17" spans="2:9" ht="15.75">
       <c r="B17" s="7" t="s">
@@ -5837,7 +5797,7 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="I17" s="16"/>
+      <c r="I17" s="28"/>
     </row>
     <row r="18" spans="2:9" ht="15">
       <c r="B18" s="2" t="s">
@@ -5851,7 +5811,7 @@
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
-      <c r="I20" s="15"/>
+      <c r="I20" s="29"/>
     </row>
     <row r="21" spans="2:9" ht="15">
       <c r="B21" s="2" t="s">
@@ -5865,7 +5825,7 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="I23" s="12"/>
+      <c r="I23" s="27"/>
     </row>
     <row r="24" spans="2:9" ht="15">
       <c r="B24" s="2" t="s">
@@ -5876,7 +5836,7 @@
       <c r="B26" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I26" s="12"/>
+      <c r="I26" s="27"/>
     </row>
     <row r="27" spans="2:9">
       <c r="B27" t="s">
